--- a/results/Int Task Remove ACC 0.2/Rando_7_permute.xlsx
+++ b/results/Int Task Remove ACC 0.2/Rando_7_permute.xlsx
@@ -440,237 +440,237 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7417201736107837</v>
+        <v>0.7366256211048359</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7379102591904658</v>
+        <v>0.7403766071726019</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7345438788370215</v>
+        <v>0.7391131832938906</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.735195233560561</v>
+        <v>0.7574328295352046</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.733359026095046</v>
+        <v>0.7769176857343101</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7422521002064849</v>
+        <v>0.7744104807610714</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7179115477571083</v>
+        <v>0.756791296203757</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7131540654277569</v>
+        <v>0.7635240569106457</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7202910746331515</v>
+        <v>0.7637794131050371</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7219882111866441</v>
+        <v>0.7651819078957707</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.727940367650063</v>
+        <v>0.7480078288280643</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7282758664039248</v>
+        <v>0.7381165084243972</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7285917223736027</v>
+        <v>0.7393995750872926</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.732568600459484</v>
+        <v>0.7390837191176147</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7347599494630448</v>
+        <v>0.7390837191176147</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7609072452016608</v>
+        <v>0.7266950151328009</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7609268879858446</v>
+        <v>0.7408201412394754</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7577977924653423</v>
+        <v>0.7050270598994919</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7555671578934136</v>
+        <v>0.702816068111747</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7552611233158277</v>
+        <v>0.6494725519590927</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7717068479459933</v>
+        <v>0.6438853584258115</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7957005088266815</v>
+        <v>0.6285738081544268</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7909037409289623</v>
+        <v>0.6328076138574343</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7883081434268959</v>
+        <v>0.6173306713432207</v>
       </c>
     </row>
     <row r="26">
@@ -680,37 +680,37 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7908742767526864</v>
+        <v>0.6068092104229328</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7793152839718024</v>
+        <v>0.6241518245789373</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7744203021531635</v>
+        <v>0.6213876919885726</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7645191603574044</v>
+        <v>0.5811301986592621</v>
       </c>
     </row>
     <row r="30">
@@ -720,607 +720,607 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7645191603574044</v>
+        <v>0.5811301986592621</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7613606006606262</v>
+        <v>0.6001322352231263</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.7252599133203219</v>
+        <v>0.5997279867246208</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6854883824717222</v>
+        <v>0.5858990738034402</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6683618389417411</v>
+        <v>0.5858990738034402</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6683618389417411</v>
+        <v>0.5833132976934657</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6785690153150861</v>
+        <v>0.5500403855642823</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6500194070707738</v>
+        <v>0.5731878353023261</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6471374177753054</v>
+        <v>0.5787848502276991</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6658039555853079</v>
+        <v>0.5259076537715717</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.665497921007722</v>
+        <v>0.5131539868566203</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.665497921007722</v>
+        <v>0.511594349792415</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6580548772247418</v>
+        <v>0.515011408529054</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6246790369064343</v>
+        <v>0.5256326547929965</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6515134372358046</v>
+        <v>0.5036653435287241</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6577225213163493</v>
+        <v>0.5470373967182407</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5712471282249523</v>
+        <v>0.5263170093939651</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5620268053290087</v>
+        <v>0.4778260466461125</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5829322276802972</v>
+        <v>0.5252484419343586</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5677499269288429</v>
+        <v>0.5295427474126525</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5833070120025268</v>
+        <v>0.5059977277227257</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.58839999308574</v>
+        <v>0.4800747525794904</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5730310858845382</v>
+        <v>0.4962505853549686</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5726268373860326</v>
+        <v>0.4968822972943243</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5679282834092331</v>
+        <v>0.4890546477970225</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5548784033087877</v>
+        <v>0.490259143323182</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5789144926033132</v>
+        <v>0.482727707011374</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5711163072822872</v>
+        <v>0.4882544007693686</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5665159672264074</v>
+        <v>0.4882544007693686</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5790225279163249</v>
+        <v>0.4901495365874355</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5717790548206536</v>
+        <v>0.4966548338534743</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5816031969024115</v>
+        <v>0.5006627475383663</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5633016220225467</v>
+        <v>0.4861644085321969</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5222159889120412</v>
+        <v>0.4834002759418322</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5309813849262845</v>
+        <v>0.4872298331463341</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5305280294673191</v>
+        <v>0.493229525147478</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5305280294673191</v>
+        <v>0.4928743836094323</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.534822334945613</v>
+        <v>0.4925487062476625</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5178757193187569</v>
+        <v>0.493496274156696</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5150361584371258</v>
+        <v>0.493496274156696</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.4951568751316067</v>
+        <v>0.4963880848442563</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.4667168736230408</v>
+        <v>0.4932900249227646</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5288717499049289</v>
+        <v>0.4932900249227646</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5326914857173388</v>
+        <v>0.4926583129834089</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5316653466715695</v>
+        <v>0.4926583129834089</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.4686450093185368</v>
+        <v>0.4926583129834089</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.4835000612854867</v>
+        <v>0.4773483341347589</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.4934125958960724</v>
+        <v>0.4640234550557383</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5003614272289846</v>
+        <v>0.4671230863999648</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5187741802673305</v>
+        <v>0.4515282871806476</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5181621111121587</v>
+        <v>0.4901691793716195</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5181621111121587</v>
+        <v>0.4920741365817784</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5309059566350183</v>
+        <v>0.4955780164245104</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.529632711364215</v>
+        <v>0.4936828806064434</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5556374004896554</v>
+        <v>0.4949463044851548</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.559138137486918</v>
+        <v>0.4981048641819331</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.622117617848848</v>
+        <v>0.4981048641819331</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4996645012461383</v>
+        <v>0.4987365761212887</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5003060345775858</v>
+        <v>0.4987365761212887</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.4999901786079081</v>
+        <v>0.4980754000056571</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4999901786079081</v>
+        <v>0.4968119761269458</v>
       </c>
     </row>
   </sheetData>
